--- a/CU-Batch_4-Dotnet-6929254-TahmidNoor.xlsx
+++ b/CU-Batch_4-Dotnet-6929254-TahmidNoor.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tahmi\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CU-DotNet-Jan26-B4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF031358-68BA-4FD5-86A7-B2598FE79A9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{304646BC-12AA-4489-90DA-2B6958A208F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C99DFE55-A9F3-4CE7-8732-71313EE2B406}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="80">
   <si>
     <t>SNO</t>
   </si>
@@ -247,13 +247,40 @@
   </si>
   <si>
     <t>https://github.com/tahmidnoor/CU-DotNet-Jan26-B4/tree/beeb872756678d170b7e6f5aa3a6da8c5ba55ff6/Week%207/Day%2038</t>
+  </si>
+  <si>
+    <t>Day47-01-Cargo.docx</t>
+  </si>
+  <si>
+    <t>Day48-01-EntryWebForm.txt</t>
+  </si>
+  <si>
+    <t>Day49-01-CollageMgmt.txt</t>
+  </si>
+  <si>
+    <t>Day50-01-StudentsDictionary.txt</t>
+  </si>
+  <si>
+    <t>Day51-01-StreamCollection.docx</t>
+  </si>
+  <si>
+    <t>https://github.com/tahmidnoor/CU-DotNet-Jan26-B4/tree/main/Week%209/Day%2047</t>
+  </si>
+  <si>
+    <t>https://github.com/tahmidnoor/CU-DotNet-Jan26-B4/tree/main/Week%209/Day%2048</t>
+  </si>
+  <si>
+    <t>https://github.com/tahmidnoor/CU-DotNet-Jan26-B4/tree/main/Week%209/Day%2050</t>
+  </si>
+  <si>
+    <t>https://github.com/tahmidnoor/CU-DotNet-Jan26-B4/tree/main/Week%209/Day%2051</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -279,6 +306,12 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -320,7 +353,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -335,6 +368,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -650,7 +684,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E48ED98-B4C9-4546-A948-8E03A0929C33}">
-  <dimension ref="A1:F39"/>
+  <dimension ref="A1:F44"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.7109375" style="1"/>
@@ -1074,6 +1108,64 @@
         <v>30</v>
       </c>
       <c r="C39" s="6"/>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40" s="5">
+        <f>A39+1</f>
+        <v>39</v>
+      </c>
+      <c r="B40" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="C40" s="7" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41" s="5">
+        <f t="shared" ref="A41:A44" si="0">A40+1</f>
+        <v>40</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="C41" s="7" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42" s="5">
+        <f t="shared" si="0"/>
+        <v>41</v>
+      </c>
+      <c r="B42" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="C42" s="6"/>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43" s="5">
+        <f t="shared" si="0"/>
+        <v>42</v>
+      </c>
+      <c r="B43" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="C43" s="7" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44" s="5">
+        <f t="shared" si="0"/>
+        <v>43</v>
+      </c>
+      <c r="B44" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="C44" s="7" t="s">
+        <v>79</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -1108,6 +1200,11 @@
     <hyperlink ref="C34" r:id="rId28" xr:uid="{3BAF11D6-A9F1-45AD-BCF2-C7AC4B09705B}"/>
     <hyperlink ref="C35" r:id="rId29" xr:uid="{B976C4C9-E734-4369-A937-2070F1DB2D7F}"/>
     <hyperlink ref="C37" r:id="rId30" xr:uid="{EA1FCBB4-CA22-41B1-9499-F64CD9D3C689}"/>
+    <hyperlink ref="B40" r:id="rId31" display="https://github.com/sharadksingh67/CU-DotNet-Jan26-B4/blob/main/Exercises/Day47-01-Cargo.docx" xr:uid="{84DEB65C-7B81-491D-A189-93A7C316CD5A}"/>
+    <hyperlink ref="C40" r:id="rId32" xr:uid="{4E8AEF58-4230-482B-9580-A290107C55EB}"/>
+    <hyperlink ref="C41" r:id="rId33" xr:uid="{5CC2BF07-47EC-4FB5-9A79-AF458E33C8F8}"/>
+    <hyperlink ref="C43" r:id="rId34" xr:uid="{985F5DC2-C75D-4C01-A250-119BD2CDDC91}"/>
+    <hyperlink ref="C44" r:id="rId35" xr:uid="{1C179F04-2A22-4DED-8BC1-ABFE1DB70BEF}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
